--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -1618,7 +1618,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-05T08:18:57.901275+00:00</t>
+          <t>2026-08-05T08:57:37.198860+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -1618,7 +1618,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-05T08:57:37.198860+00:00</t>
+          <t>2026-08-05T09:47:40.404086+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1205,22 +1205,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Escrow (EMD)</t>
+          <t>Compliance</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>EMD held in an escrow-controlled account, not a PMC operational account</t>
+          <t>KYC as a pre-bid gate — verify before allowing bid submission</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Joint escrow accounts with TWO named officers (one PMC, one escrow institution) on file</t>
+          <t>`bids.create_bid()` returns HTTP 412 unless vendor has a passing KYC decision; `kyc_bypass` override on notices</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Wave 32</t>
+          <t>Wave 35d</t>
         </is>
       </c>
     </row>
@@ -1240,17 +1240,17 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Release requires dual authorisation from both operating officers</t>
+          <t>EMD held in an escrow-controlled account, not a PMC operational account</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>`/transactions/{id}/sign` per officer + `/release` gated by both signing the same action; 409 otherwise</t>
+          <t>Joint escrow accounts with TWO named officers (one PMC, one escrow institution) on file</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Wave 32 verified via curl</t>
+          <t>Wave 32</t>
         </is>
       </c>
     </row>
@@ -1270,47 +1270,47 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>Release requires dual authorisation from both operating officers</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>`/transactions/{id}/sign` per officer + `/release` gated by both signing the same action; 409 otherwise</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Wave 32 verified via curl</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Escrow (EMD)</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>Three outcomes: to contractor (via PMC), refund to vendor, forfeit</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>`release_to_contractor` / `release_to_vendor` / `forfeit` — all audit-logged and immutable on tx</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Wave 32</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Payments</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Stripe (EMD), PayPal, Kaspi Pay</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Stripe wired; PayPal/Kaspi in sandbox mock — waiting for merchant credentials</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Waves 1-3</t>
         </is>
       </c>
     </row>
@@ -1325,22 +1325,22 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Evaluation</t>
+          <t>Escrow (EMD)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Committee scoring with per-criterion weights</t>
+          <t>Non-PMC escrow officer signs without a full staff account</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Evaluation panel with rubric management, external committee invite by email, accept-flow</t>
+          <t>`POST /escrow/magic-tokens` admin-issued token → `/escrow/officer/:token` public portal signs the same transactions</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Waves 2-5</t>
+          <t>Wave 35b</t>
         </is>
       </c>
     </row>
@@ -1355,22 +1355,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Contracts / BOQ</t>
+          <t>Revenue Catalog</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>BOQ Builder + Contract Award workflow</t>
+          <t>Admin-editable master of every revenue line (client + supplier)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>BOQ/Contracts panel, BOQ templates, contract award pipeline</t>
+          <t>55 products seeded from CA-02/CA-03; 9 pricing models; multi-currency; live CRUD via Admin → Product Catalog</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Waves 3-4</t>
+          <t>Wave 35 · `products.py`</t>
         </is>
       </c>
     </row>
@@ -1385,22 +1385,22 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Audit</t>
+          <t>Revenue Catalog</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Every substantive action is logged and attributable</t>
+          <t>Client purchase surface — packages + services</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Global `audit_log` collection + per-transaction immutable `audit_trail[]` on escrow records</t>
+          <t>Public `/services` with 34 products, 5 category filters, quote-vs-subscribe CTAs driven by pricing_model</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Throughout</t>
+          <t>Wave 36 · `ClientPurchase`</t>
         </is>
       </c>
     </row>
@@ -1415,170 +1415,410 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>Revenue Catalog</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Supplier purchase surface — Supplier Success + tender-stage + add-ons</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Public `/vendor/services` with 21 products, GBP pricing, SME/Mid/Tier-1 subscription tiers</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Wave 37 · `VendorPurchase`</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Payments</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Stripe Checkout for one-off + subscription products from the catalog</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>`POST /api/v1/billing/checkout` (admin, vendor OR anon) creates `cs_test_...` session with server-authoritative amount; `/api/webhook/stripe` idempotent</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Wave 35 · `emergentintegrations`</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Payments</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>PayPal, Kaspi Pay</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>In sandbox mock — waiting for merchant credentials</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>P2 · blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Evaluation</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Committee scoring with per-criterion weights</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Evaluation panel with rubric management, external committee invite by email, accept-flow</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Waves 2-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Contracts / BOQ</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>BOQ Builder + Contract Award workflow</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>BOQ/Contracts panel, BOQ templates, contract award pipeline</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Waves 3-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Audit</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Every substantive action is logged and attributable</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Global `audit_log` collection + per-transaction immutable `audit_trail[]` on escrow records</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Throughout</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Live public roadmap page so vendors can see what's built vs coming</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Public `/roadmap` reads `/api/v1/reports/public/roadmap` — 20 areas, status pills, stat-card filters</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Wave 35c</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Stakeholder reports auto-regenerate on every deploy</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>`_refresh_reports_snapshot()` runs at startup — `/app/docs/reports/*.{xlsx,docx,pdf,svg}` never drifts</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Wave 35e</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
           <t>Mobile</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Mobile-friendly app for staff and vendors</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>PWA + Capacitor mobile wrapper, unified `/m` login, mobile hamburger menu</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Waves 13, 22</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Evaluation</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Technical vs commercial evaluators segregated</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Currently rubric-scored, but a firewall role split (`tech_evaluator` cannot see commercial score until joint meeting) is not enforced</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>Roadmap · P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Live push notifications on mobile</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Firebase/APNs plumbing scaffolded; waiting for `google-services.json` + APNs auth key</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>Blocked · P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Emails</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Real transactional email dispatch</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Currently console-logged; needs Emergent-managed Resend key</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>Blocked · P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>Compliance</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>KYC should be a pre-bid gate (verify before allowing bid submission)</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>Currently: KYC stub can be run, but not enforced as a gate before bidding</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>Roadmap · P1 — needs live KYC keys</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Live KYC provider integration</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Stubbed logic in place + pre-bid gate wired; awaiting `KYC_BASE_URL` and `KYC_API_KEY`</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>Blocked · P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>Evaluation</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>Technical vs commercial evaluators segregated</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>Currently rubric-scored, but a firewall role split (`tech_evaluator` cannot see commercial score until joint meeting) is not enforced</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>Roadmap · P1</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>Notifications</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>Live push notifications on mobile</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>Firebase/APNs plumbing scaffolded; waiting for `google-services.json` + APNs auth key</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>Blocked · P1</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>Emails</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>Real transactional email dispatch</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>Currently console-logged; needs Emergent-managed Resend key</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>Blocked · P2</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>Native AWS Phase 2 migration (Postgres RLS, S3, Cognito, Fargate)</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E45" s="4" t="inlineStr">
         <is>
           <t>MongoDB + FastAPI on Emergent for MVP; portability was a design constraint</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="F45" s="4" t="inlineStr">
         <is>
           <t>Roadmap · P2</t>
         </is>
@@ -1618,7 +1858,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-05T09:47:40.404086+00:00</t>
+          <t>2026-08-05T10:00:19.084296+00:00</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1869,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5">
@@ -1639,11 +1879,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>86%</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1898,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2%</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1913,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>11%</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-05T10:00:19.084296+00:00</t>
+          <t>2026-08-05T10:16:27.145353+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-05T10:16:27.145353+00:00</t>
+          <t>2026-08-05T10:19:52.136365+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1420,17 +1420,17 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Supplier purchase surface — Supplier Success + tender-stage + add-ons</t>
+          <t>Quote pipeline — Request quote → engagement → admin quote → invoice → paid</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Public `/vendor/services` with 21 products, GBP pricing, SME/Mid/Tier-1 subscription tiers</t>
+          <t>New `engagements.py` router + `EngagementsPanel.jsx` admin UI. Quote requests from purchase pages land in a persistent pipeline; admin sets amount, generates Stripe pay-link in one click; end-to-end tested $40k USD.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Wave 37 · `VendorPurchase`</t>
+          <t>Wave 38</t>
         </is>
       </c>
     </row>
@@ -1445,82 +1445,82 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>Revenue Catalog</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Supplier purchase surface — Supplier Success + tender-stage + add-ons</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Public `/vendor/services` with 21 products, GBP pricing, SME/Mid/Tier-1 subscription tiers</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Wave 37 · `VendorPurchase`</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
           <t>Payments</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Stripe Checkout for one-off + subscription products from the catalog</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>`POST /api/v1/billing/checkout` (admin, vendor OR anon) creates `cs_test_...` session with server-authoritative amount; `/api/webhook/stripe` idempotent</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Wave 35 · `emergentintegrations`</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>Payments</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>PayPal, Kaspi Pay</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>In sandbox mock — waiting for merchant credentials</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>P2 · blocked</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Evaluation</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Committee scoring with per-criterion weights</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Evaluation panel with rubric management, external committee invite by email, accept-flow</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Waves 2-5</t>
         </is>
       </c>
     </row>
@@ -1535,22 +1535,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Contracts / BOQ</t>
+          <t>Evaluation</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>BOQ Builder + Contract Award workflow</t>
+          <t>Committee scoring with per-criterion weights</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>BOQ/Contracts panel, BOQ templates, contract award pipeline</t>
+          <t>Evaluation panel with rubric management, external committee invite by email, accept-flow</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Waves 3-4</t>
+          <t>Waves 2-5</t>
         </is>
       </c>
     </row>
@@ -1565,22 +1565,22 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Audit</t>
+          <t>Contracts / BOQ</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Every substantive action is logged and attributable</t>
+          <t>BOQ Builder + Contract Award workflow</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Global `audit_log` collection + per-transaction immutable `audit_trail[]` on escrow records</t>
+          <t>BOQ/Contracts panel, BOQ templates, contract award pipeline</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Throughout</t>
+          <t>Waves 3-4</t>
         </is>
       </c>
     </row>
@@ -1595,22 +1595,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Audit</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Live public roadmap page so vendors can see what's built vs coming</t>
+          <t>Every substantive action is logged and attributable</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Public `/roadmap` reads `/api/v1/reports/public/roadmap` — 20 areas, status pills, stat-card filters</t>
+          <t>Global `audit_log` collection + per-transaction immutable `audit_trail[]` on escrow records</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Wave 35c</t>
+          <t>Throughout</t>
         </is>
       </c>
     </row>
@@ -1630,17 +1630,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Stakeholder reports auto-regenerate on every deploy</t>
+          <t>Live public roadmap page so vendors can see what's built vs coming</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>`_refresh_reports_snapshot()` runs at startup — `/app/docs/reports/*.{xlsx,docx,pdf,svg}` never drifts</t>
+          <t>Public `/roadmap` reads `/api/v1/reports/public/roadmap` — 20 areas, status pills, stat-card filters</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Wave 35e</t>
+          <t>Wave 35c</t>
         </is>
       </c>
     </row>
@@ -1655,52 +1655,52 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Stakeholder reports auto-regenerate on every deploy</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>`_refresh_reports_snapshot()` runs at startup — `/app/docs/reports/*.{xlsx,docx,pdf,svg}` never drifts</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Wave 35e</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
           <t>Mobile</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Mobile-friendly app for staff and vendors</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>PWA + Capacitor mobile wrapper, unified `/m` login, mobile hamburger menu</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Waves 13, 22</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>Evaluation</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>Technical vs commercial evaluators segregated</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>Currently rubric-scored, but a firewall role split (`tech_evaluator` cannot see commercial score until joint meeting) is not enforced</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>Roadmap · P1</t>
         </is>
       </c>
     </row>
@@ -1715,22 +1715,22 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Evaluation</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Live push notifications on mobile</t>
+          <t>Technical vs commercial evaluators segregated</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Firebase/APNs plumbing scaffolded; waiting for `google-services.json` + APNs auth key</t>
+          <t>Currently rubric-scored, but a firewall role split (`tech_evaluator` cannot see commercial score until joint meeting) is not enforced</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Blocked · P1</t>
+          <t>Roadmap · P1</t>
         </is>
       </c>
     </row>
@@ -1745,22 +1745,22 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Emails</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Real transactional email dispatch</t>
+          <t>Live push notifications on mobile</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Currently console-logged; needs Emergent-managed Resend key</t>
+          <t>Firebase/APNs plumbing scaffolded; waiting for `google-services.json` + APNs auth key</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Blocked · P2</t>
+          <t>Blocked · P1</t>
         </is>
       </c>
     </row>
@@ -1775,22 +1775,22 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Compliance</t>
+          <t>Emails</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Live KYC provider integration</t>
+          <t>Real transactional email dispatch</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Stubbed logic in place + pre-bid gate wired; awaiting `KYC_BASE_URL` and `KYC_API_KEY`</t>
+          <t>Currently console-logged; needs Emergent-managed Resend key</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Blocked · P1</t>
+          <t>Blocked · P2</t>
         </is>
       </c>
     </row>
@@ -1805,20 +1805,50 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Live KYC provider integration</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Stubbed logic in place + pre-bid gate wired; awaiting `KYC_BASE_URL` and `KYC_API_KEY`</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>Blocked · P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>Native AWS Phase 2 migration (Postgres RLS, S3, Cognito, Fargate)</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
+      <c r="E46" s="4" t="inlineStr">
         <is>
           <t>MongoDB + FastAPI on Emergent for MVP; portability was a design constraint</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="F46" s="4" t="inlineStr">
         <is>
           <t>Roadmap · P2</t>
         </is>
@@ -1858,7 +1888,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-05T10:19:52.136365+00:00</t>
+          <t>2026-08-05T10:34:10.739335+00:00</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1899,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5">
@@ -1879,11 +1909,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>87%</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -1888,7 +1888,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-05T10:34:10.739335+00:00</t>
+          <t>2026-08-05T10:35:44.786651+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -1888,7 +1888,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-05T10:35:44.786651+00:00</t>
+          <t>2026-08-05T10:43:02.255074+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -1888,7 +1888,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-05T10:43:02.255074+00:00</t>
+          <t>2026-08-05T10:59:16.116419+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -1888,7 +1888,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-05T10:59:16.116419+00:00</t>
+          <t>2026-08-06T04:22:22.562718+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -1888,7 +1888,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-06T04:22:22.562718+00:00</t>
+          <t>2026-08-06T09:38:55.266118+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1705,122 +1705,122 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="n">
+      <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Formal corrigendum / amendment publisher for published notices</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>New `/api/v1/notices/{ref}/corrigenda` router — auto-numbered, deadline auto-update on parent notice, public banner on Notice Detail, admin CorrigendaPanel with withdraw</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Wave 39</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Bidding</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Two-cover / split-envelope submission — technical clearance before commercial visibility</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>New `/bids/{id}/technical-clear` + `/financial-open`; `_redact_commercial()` strips price and commercial docs for tech-only viewers or before financial open</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Wave 39</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Post-Award</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Auto-generated Purchase Order, SLA, and Contract on bid award</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>New `/api/v1/awards/*` router — 3 WeasyPrint PDFs (PO/SLA/Contract) drafted on award, stored in `award_documents`, downloadable by admin + awarded vendor, admin AwardsPanel with regenerate</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Wave 39 · PMC-PO-YYYY-##### numbering</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>Evaluation</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>Technical vs commercial evaluators segregated</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>Currently rubric-scored, but a firewall role split (`tech_evaluator` cannot see commercial score until joint meeting) is not enforced</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>Roadmap · P1</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>Notifications</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>Live push notifications on mobile</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>Firebase/APNs plumbing scaffolded; waiting for `google-services.json` + APNs auth key</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>Blocked · P1</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>Emails</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>Real transactional email dispatch</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>Currently console-logged; needs Emergent-managed Resend key</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>Blocked · P2</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>Compliance</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>Live KYC provider integration</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>Stubbed logic in place + pre-bid gate wired; awaiting `KYC_BASE_URL` and `KYC_API_KEY`</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>Blocked · P1</t>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Technical vs commercial evaluators segregated (role firewall)</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>`tech_evaluator` role sees redacted bids (price + commercial notes + commercial documents stripped); commercial envelope gated by explicit `financial-open` after `technical-clear`</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Wave 39 · supersedes earlier planned row</t>
         </is>
       </c>
     </row>
@@ -1835,20 +1835,290 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
+          <t>Bidding</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Live Reverse Auction room with masked identities, auto-bid, price floor</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>Auction model + endpoints scaffolded (`auction_type = reverse|forward|live|sealed`); missing real-time WebSocket bidding UI, auto-bid engine, masked leaderboard, price-floor validator</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>Roadmap · P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>L1 (lowest-price) auto-comparison for mid-value tenders</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Rule-based engine that fires when ≥ N vendors submit against a mid-value tender and auto-shortlists lowest-price compliant bid</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Roadmap · P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Direct-Purchase value-threshold gate</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Config flag on notice/product so low-value catalog items skip full tender workflow and issue a direct PO</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>Roadmap · P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Taxonomy</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>UNSPSC / standardised product &amp; service classification</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Import UNSPSC v25 seed into `taxonomy_nodes`, add `unspsc_code` to products / BOQ items / registration scopes, expose a picker widget</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>Roadmap · P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>PKI / DSC (Digital Signature Certificate) integration for bid + contract signing</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Research done — shortlist: DocuSign eSignature Advanced (UK/EU global), Signicat (UK/EU eIDAS), eMudhra emSigner (India + global) or Adobe Sign Cloud Signatures. Needs paid vendor account + PKCS#11 handler on frontend</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>Roadmap · P1 · Legal non-repudiation</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Scheduled Pre-Bid Meeting rooms (video + invitees)</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Q&amp;A thread already live (Wave 31); missing formal meeting scheduler with Google Meet / MS Teams link, RSVP list, minutes upload</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>Roadmap · P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>Live push notifications on mobile</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>Firebase/APNs plumbing scaffolded; waiting for `google-services.json` + APNs auth key</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>Blocked · P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Emails</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Real transactional email dispatch</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Currently console-logged; needs Emergent-managed Resend key</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>Blocked · P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>Live KYC provider integration</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>Stubbed logic in place + pre-bid gate wired; awaiting `KYC_BASE_URL` and `KYC_API_KEY`</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>Blocked · P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>Native AWS Phase 2 migration (Postgres RLS, S3, Cognito, Fargate)</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="E55" s="4" t="inlineStr">
         <is>
           <t>MongoDB + FastAPI on Emergent for MVP; portability was a design constraint</t>
         </is>
       </c>
-      <c r="F46" s="4" t="inlineStr">
+      <c r="F55" s="4" t="inlineStr">
         <is>
           <t>Roadmap · P2</t>
         </is>
@@ -1888,7 +2158,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-06T09:38:55.266118+00:00</t>
+          <t>2026-08-06T09:59:15.810165+00:00</t>
         </is>
       </c>
     </row>
@@ -1899,7 +2169,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5">
@@ -1909,11 +2179,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>80%</t>
         </is>
       </c>
     </row>
@@ -1939,11 +2209,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>19%</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1715,22 +1715,22 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Bidding</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Formal corrigendum / amendment publisher for published notices</t>
+          <t>Live Reverse Auction room with masked identities, auto-bid, price floor, anti-snipe</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>New `/api/v1/notices/{ref}/corrigenda` router — auto-numbered, deadline auto-update on parent notice, public banner on Notice Detail, admin CorrigendaPanel with withdraw</t>
+          <t>New `/api/v1/reverse-auctions/*` router · masked `Bidder A/B/C…` aliases · min-decrement + hard floor enforced · anti-snipe extends close time on last-second bids · auto-bid cascade lets pre-armed bidders undercut competitors automatically. Admin LiveAuctionsPanel + public `/vendor/auction/:aid` room with 2s polling</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Wave 39</t>
+          <t>Wave 40</t>
         </is>
       </c>
     </row>
@@ -1745,22 +1745,22 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Bidding</t>
+          <t>Taxonomy</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Two-cover / split-envelope submission — technical clearance before commercial visibility</t>
+          <t>UNSPSC / standardised product &amp; service classification</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>New `/bids/{id}/technical-clear` + `/financial-open`; `_redact_commercial()` strips price and commercial docs for tech-only viewers or before financial open</t>
+          <t>New `/api/v1/taxonomy/*` router + curated UNSPSC-lite seed (87 nodes across 23 segments: Construction, Medical, IT/Telecom, Professional Services, Utilities, Facilities, Education). Search + tree + lookup-chain endpoints. Idempotent startup seed</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Wave 39</t>
+          <t>Wave 40 · products/BOQ can now be tagged</t>
         </is>
       </c>
     </row>
@@ -1775,22 +1775,22 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Post-Award</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Auto-generated Purchase Order, SLA, and Contract on bid award</t>
+          <t>Formal corrigendum / amendment publisher for published notices</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>New `/api/v1/awards/*` router — 3 WeasyPrint PDFs (PO/SLA/Contract) drafted on award, stored in `award_documents`, downloadable by admin + awarded vendor, admin AwardsPanel with regenerate</t>
+          <t>New `/api/v1/notices/{ref}/corrigenda` router — auto-numbered, deadline auto-update on parent notice, public banner on Notice Detail, admin CorrigendaPanel with withdraw</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Wave 39 · PMC-PO-YYYY-##### numbering</t>
+          <t>Wave 39</t>
         </is>
       </c>
     </row>
@@ -1805,82 +1805,82 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>Bidding</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Two-cover / split-envelope submission — technical clearance before commercial visibility</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>New `/bids/{id}/technical-clear` + `/financial-open`; `_redact_commercial()` strips price and commercial docs for tech-only viewers or before financial open</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Wave 39</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Post-Award</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Auto-generated Purchase Order, SLA, and Contract on bid award</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>New `/api/v1/awards/*` router — 3 WeasyPrint PDFs (PO/SLA/Contract) drafted on award, stored in `award_documents`, downloadable by admin + awarded vendor, admin AwardsPanel with regenerate</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Wave 39 · PMC-PO-YYYY-##### numbering</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
           <t>Evaluation</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Technical vs commercial evaluators segregated (role firewall)</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>`tech_evaluator` role sees redacted bids (price + commercial notes + commercial documents stripped); commercial envelope gated by explicit `financial-open` after `technical-clear`</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Wave 39 · supersedes earlier planned row</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>Bidding</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>Live Reverse Auction room with masked identities, auto-bid, price floor</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>Auction model + endpoints scaffolded (`auction_type = reverse|forward|live|sealed`); missing real-time WebSocket bidding UI, auto-bid engine, masked leaderboard, price-floor validator</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>Roadmap · P1</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>Procurement</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>L1 (lowest-price) auto-comparison for mid-value tenders</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>Rule-based engine that fires when ≥ N vendors submit against a mid-value tender and auto-shortlists lowest-price compliant bid</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>Roadmap · P2</t>
         </is>
       </c>
     </row>
@@ -1895,17 +1895,17 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Bidding</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Direct-Purchase value-threshold gate</t>
+          <t>L1 (lowest-price) auto-comparison for mid-value tenders</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Config flag on notice/product so low-value catalog items skip full tender workflow and issue a direct PO</t>
+          <t>Rule-based engine that fires when ≥ N vendors submit against a mid-value tender and auto-shortlists lowest-price compliant bid</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -1925,22 +1925,22 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>UNSPSC / standardised product &amp; service classification</t>
+          <t>Direct-Purchase value-threshold gate</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Import UNSPSC v25 seed into `taxonomy_nodes`, add `unspsc_code` to products / BOQ items / registration scopes, expose a picker widget</t>
+          <t>Config flag on notice/product so low-value catalog items skip full tender workflow and issue a direct PO</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Roadmap · P1</t>
+          <t>Roadmap · P2</t>
         </is>
       </c>
     </row>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Taxonomy</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>PKI / DSC (Digital Signature Certificate) integration for bid + contract signing</t>
+          <t>UNSPSC picker widget in Product Catalog + BOQ Builder + registration scopes</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Research done — shortlist: DocuSign eSignature Advanced (UK/EU global), Signicat (UK/EU eIDAS), eMudhra emSigner (India + global) or Adobe Sign Cloud Signatures. Needs paid vendor account + PKCS#11 handler on frontend</t>
+          <t>Backend + seed shipped in Wave 40; frontend picker widgets still to be attached to product/BOQ/registration edit forms</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Roadmap · P1 · Legal non-repudiation</t>
+          <t>Roadmap · P2</t>
         </is>
       </c>
     </row>
@@ -1985,22 +1985,22 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Scheduled Pre-Bid Meeting rooms (video + invitees)</t>
+          <t>PKI / DSC (Digital Signature Certificate) integration for bid + contract signing</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Q&amp;A thread already live (Wave 31); missing formal meeting scheduler with Google Meet / MS Teams link, RSVP list, minutes upload</t>
+          <t>Research done — shortlist: DocuSign eSignature Advanced (UK/EU global), Signicat (UK/EU eIDAS), eMudhra emSigner (India + global) or Adobe Sign Cloud Signatures. Needs paid vendor account + PKCS#11 handler on frontend</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Roadmap · P2</t>
+          <t>Roadmap · P1 · Legal non-repudiation</t>
         </is>
       </c>
     </row>
@@ -2015,22 +2015,22 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Live push notifications on mobile</t>
+          <t>Scheduled Pre-Bid Meeting rooms (video + invitees)</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Firebase/APNs plumbing scaffolded; waiting for `google-services.json` + APNs auth key</t>
+          <t>Q&amp;A thread already live (Wave 31); missing formal meeting scheduler with Google Meet / MS Teams link, RSVP list, minutes upload</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Blocked · P1</t>
+          <t>Roadmap · P2</t>
         </is>
       </c>
     </row>
@@ -2045,22 +2045,22 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Emails</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Real transactional email dispatch</t>
+          <t>Live push notifications on mobile</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Currently console-logged; needs Emergent-managed Resend key</t>
+          <t>Firebase/APNs plumbing scaffolded; waiting for `google-services.json` + APNs auth key</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Blocked · P2</t>
+          <t>Blocked · P1</t>
         </is>
       </c>
     </row>
@@ -2075,22 +2075,22 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Compliance</t>
+          <t>Emails</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Live KYC provider integration</t>
+          <t>Real transactional email dispatch</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Stubbed logic in place + pre-bid gate wired; awaiting `KYC_BASE_URL` and `KYC_API_KEY`</t>
+          <t>Currently console-logged; needs Emergent-managed Resend key</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Blocked · P1</t>
+          <t>Blocked · P2</t>
         </is>
       </c>
     </row>
@@ -2105,20 +2105,50 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>Live KYC provider integration</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Stubbed logic in place + pre-bid gate wired; awaiting `KYC_BASE_URL` and `KYC_API_KEY`</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>Blocked · P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>Native AWS Phase 2 migration (Postgres RLS, S3, Cognito, Fargate)</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
+      <c r="E56" s="4" t="inlineStr">
         <is>
           <t>MongoDB + FastAPI on Emergent for MVP; portability was a design constraint</t>
         </is>
       </c>
-      <c r="F55" s="4" t="inlineStr">
+      <c r="F56" s="4" t="inlineStr">
         <is>
           <t>Roadmap · P2</t>
         </is>
@@ -2158,7 +2188,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-06T09:59:15.810165+00:00</t>
+          <t>2026-08-06T10:24:25.750063+00:00</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2199,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
@@ -2179,11 +2209,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>82%</t>
         </is>
       </c>
     </row>
@@ -2209,11 +2239,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>16%</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-06T10:24:25.750063+00:00</t>
+          <t>2026-08-07T01:39:11.685760+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-07T01:39:11.685760+00:00</t>
+          <t>2026-08-07T02:48:24.425755+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-07T02:48:24.425755+00:00</t>
+          <t>2026-08-07T12:50:46.830327+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-07T12:50:46.830327+00:00</t>
+          <t>2026-08-07T13:06:08.893504+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-07T13:06:08.893504+00:00</t>
+          <t>2026-08-07T13:40:34.797024+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-07T13:40:34.797024+00:00</t>
+          <t>2026-08-07T14:48:12.895599+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-07T14:48:12.895599+00:00</t>
+          <t>2026-08-07T15:14:53.910595+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1715,22 +1715,22 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Bidding</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Live Reverse Auction room with masked identities, auto-bid, price floor, anti-snipe</t>
+          <t>PKI / DSC (Digital Signature Certificate) integration for bid + contract signing</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>New `/api/v1/reverse-auctions/*` router · masked `Bidder A/B/C…` aliases · min-decrement + hard floor enforced · anti-snipe extends close time on last-second bids · auto-bid cascade lets pre-armed bidders undercut competitors automatically. Admin LiveAuctionsPanel + public `/vendor/auction/:aid` room with 2s polling</t>
+          <t>DocuSign eSignature via JWT Grant (sandbox). New `/api/v1/docusign/*` router — envelope creation from Award PDFs (PO/SLA/Contract) + Bid acknowledgements, embedded signing view, Connect webhook for status. Admin DocuSignPanel with consent flow + envelope log. Trilingual (EN/RU/KK)</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Wave 40</t>
+          <t>Wave 43 · consent granted, sandbox live</t>
         </is>
       </c>
     </row>
@@ -1745,22 +1745,22 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Taxonomy</t>
+          <t>i18n</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>UNSPSC / standardised product &amp; service classification</t>
+          <t>Trilingual coverage across every admin panel (not just public + login)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>New `/api/v1/taxonomy/*` router + curated UNSPSC-lite seed (87 nodes across 23 segments: Construction, Medical, IT/Telecom, Professional Services, Utilities, Facilities, Education). Search + tree + lookup-chain endpoints. Idempotent startup seed</t>
+          <t>Added `panels` namespace to `i18n-strings.js` — ~450 EN/RU/KK strings covering headings, buttons, filter chips, table headers, empty states and toasts for 15 admin panels (Analytics, Audit, Awards, BOQ, Bidding, Corrigenda, Engagements, Evaluation, LiveAuctions, MFA, Masters, Permissions, Reports, TenderBuilder, VendorIntel). 21 of 22 admin panels now use `useI18n`</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Wave 40 · products/BOQ can now be tagged</t>
+          <t>Wave 42a</t>
         </is>
       </c>
     </row>
@@ -1775,22 +1775,22 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>UX / Mobile</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Formal corrigendum / amendment publisher for published notices</t>
+          <t>Mobile-first responsive layout across top pages</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>New `/api/v1/notices/{ref}/corrigenda` router — auto-numbered, deadline auto-update on parent notice, public banner on Notice Detail, admin CorrigendaPanel with withdraw</t>
+          <t>Home@375px now renders at exact viewport (was 421 overflow) via responsive stat cards + `overflow-x-hidden`. AdminDashboard's 22-tab bar collapses into a mobile `&lt;select&gt;` on md-, header buttons stack + adaptive text sizes. Every admin function reachable at 375/768 viewport with zero horizontal scroll</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Wave 39</t>
+          <t>Wave 42b</t>
         </is>
       </c>
     </row>
@@ -1805,22 +1805,22 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Bidding</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Two-cover / split-envelope submission — technical clearance before commercial visibility</t>
+          <t>Scheduled Pre-Bid Meeting rooms (video + invitees + minutes)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>New `/bids/{id}/technical-clear` + `/financial-open`; `_redact_commercial()` strips price and commercial docs for tech-only viewers or before financial open</t>
+          <t>New `/api/v1/meetings` router with dual provider (Jitsi iframe by default, Zoom via S2S OAuth for enterprise). Admin MeetingsPanel + shared MeetingRoom.jsx. RSVP-style invitee list, minutes upload, cancel flow</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Wave 39</t>
+          <t>Wave 41a + 41b</t>
         </is>
       </c>
     </row>
@@ -1835,22 +1835,22 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Post-Award</t>
+          <t>Bidding</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Auto-generated Purchase Order, SLA, and Contract on bid award</t>
+          <t>L1 (lowest-price) auto-comparison for mid-value tenders</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>New `/api/v1/awards/*` router — 3 WeasyPrint PDFs (PO/SLA/Contract) drafted on award, stored in `award_documents`, downloadable by admin + awarded vendor, admin AwardsPanel with regenerate</t>
+          <t>New `/api/v1/comparison/l1/{notice_ref}` — automatic ranking of commercial bids per notice with tie-break rules, exposed on admin L1ComparisonPanel</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Wave 39 · PMC-PO-YYYY-##### numbering</t>
+          <t>Wave 41a</t>
         </is>
       </c>
     </row>
@@ -1865,172 +1865,172 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>Bidding</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Live Reverse Auction room with masked identities, auto-bid, price floor, anti-snipe</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>New `/api/v1/reverse-auctions/*` router · masked `Bidder A/B/C…` aliases · min-decrement + hard floor enforced · anti-snipe extends close time on last-second bids · auto-bid cascade lets pre-armed bidders undercut competitors automatically. Admin LiveAuctionsPanel + public `/vendor/auction/:aid` room with 2s polling</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Wave 40</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Taxonomy</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC / standardised product &amp; service classification</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>New `/api/v1/taxonomy/*` router + curated UNSPSC-lite seed (87 nodes across 23 segments: Construction, Medical, IT/Telecom, Professional Services, Utilities, Facilities, Education). Search + tree + lookup-chain endpoints. Idempotent startup seed</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Wave 40 · products/BOQ can now be tagged</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Formal corrigendum / amendment publisher for published notices</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>New `/api/v1/notices/{ref}/corrigenda` router — auto-numbered, deadline auto-update on parent notice, public banner on Notice Detail, admin CorrigendaPanel with withdraw</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Wave 39</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Bidding</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Two-cover / split-envelope submission — technical clearance before commercial visibility</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>New `/bids/{id}/technical-clear` + `/financial-open`; `_redact_commercial()` strips price and commercial docs for tech-only viewers or before financial open</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Wave 39</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Post-Award</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Auto-generated Purchase Order, SLA, and Contract on bid award</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>New `/api/v1/awards/*` router — 3 WeasyPrint PDFs (PO/SLA/Contract) drafted on award, stored in `award_documents`, downloadable by admin + awarded vendor, admin AwardsPanel with regenerate</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Wave 39 · PMC-PO-YYYY-##### numbering</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
           <t>Evaluation</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Technical vs commercial evaluators segregated (role firewall)</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>`tech_evaluator` role sees redacted bids (price + commercial notes + commercial documents stripped); commercial envelope gated by explicit `financial-open` after `technical-clear`</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Wave 39 · supersedes earlier planned row</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>Bidding</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>L1 (lowest-price) auto-comparison for mid-value tenders</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>Rule-based engine that fires when ≥ N vendors submit against a mid-value tender and auto-shortlists lowest-price compliant bid</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>Roadmap · P2</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>Procurement</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>Direct-Purchase value-threshold gate</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>Config flag on notice/product so low-value catalog items skip full tender workflow and issue a direct PO</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>Roadmap · P2</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>Taxonomy</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>UNSPSC picker widget in Product Catalog + BOQ Builder + registration scopes</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>Backend + seed shipped in Wave 40; frontend picker widgets still to be attached to product/BOQ/registration edit forms</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>Roadmap · P2</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>Legal</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>PKI / DSC (Digital Signature Certificate) integration for bid + contract signing</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>Research done — shortlist: DocuSign eSignature Advanced (UK/EU global), Signicat (UK/EU eIDAS), eMudhra emSigner (India + global) or Adobe Sign Cloud Signatures. Needs paid vendor account + PKCS#11 handler on frontend</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>Roadmap · P1 · Legal non-repudiation</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>Procurement</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>Scheduled Pre-Bid Meeting rooms (video + invitees)</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>Q&amp;A thread already live (Wave 31); missing formal meeting scheduler with Google Meet / MS Teams link, RSVP list, minutes upload</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>Roadmap · P2</t>
         </is>
       </c>
     </row>
@@ -2045,22 +2045,22 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Live push notifications on mobile</t>
+          <t>Direct-Purchase value-threshold gate</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Firebase/APNs plumbing scaffolded; waiting for `google-services.json` + APNs auth key</t>
+          <t>Config flag on notice/product so low-value catalog items skip full tender workflow and issue a direct PO</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Blocked · P1</t>
+          <t>Roadmap · P2</t>
         </is>
       </c>
     </row>
@@ -2075,22 +2075,22 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Emails</t>
+          <t>Taxonomy</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Real transactional email dispatch</t>
+          <t>UNSPSC picker widget in Product Catalog + BOQ Builder + registration scopes</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Currently console-logged; needs Emergent-managed Resend key</t>
+          <t>Backend + seed shipped in Wave 40; frontend picker widgets still to be attached to product/BOQ/registration edit forms</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Blocked · P2</t>
+          <t>Roadmap · P2</t>
         </is>
       </c>
     </row>
@@ -2105,17 +2105,17 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Compliance</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Live KYC provider integration</t>
+          <t>Live push notifications on mobile</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Stubbed logic in place + pre-bid gate wired; awaiting `KYC_BASE_URL` and `KYC_API_KEY`</t>
+          <t>Firebase/APNs plumbing scaffolded; waiting for `google-services.json` + APNs auth key</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -2135,20 +2135,80 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
+          <t>Emails</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>Real transactional email dispatch</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Currently console-logged; needs Emergent-managed Resend key</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>Blocked · P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Live KYC provider integration</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Stubbed logic in place + pre-bid gate wired; awaiting `KYC_BASE_URL` and `KYC_API_KEY`</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>Blocked · P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D58" s="4" t="inlineStr">
         <is>
           <t>Native AWS Phase 2 migration (Postgres RLS, S3, Cognito, Fargate)</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
+      <c r="E58" s="4" t="inlineStr">
         <is>
           <t>MongoDB + FastAPI on Emergent for MVP; portability was a design constraint</t>
         </is>
       </c>
-      <c r="F56" s="4" t="inlineStr">
+      <c r="F58" s="4" t="inlineStr">
         <is>
           <t>Roadmap · P2</t>
         </is>
@@ -2188,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-07T15:14:53.910595+00:00</t>
+          <t>2026-08-07T16:00:59.410132+00:00</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2259,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5">
@@ -2209,11 +2269,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>88%</t>
         </is>
       </c>
     </row>
@@ -2239,11 +2299,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>11%</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-07T16:00:59.410132+00:00</t>
+          <t>2026-08-07T16:08:58.312232+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-07T16:08:58.312232+00:00</t>
+          <t>2026-08-08T01:58:12.581200+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-08T01:58:12.581200+00:00</t>
+          <t>2026-08-08T02:09:37.564006+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-08T02:09:37.564006+00:00</t>
+          <t>2026-08-08T03:24:30.527555+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-08T03:24:30.527555+00:00</t>
+          <t>2026-08-11T02:34:35.486367+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-11T02:34:35.486367+00:00</t>
+          <t>2026-08-11T02:40:47.197812+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-11T02:40:47.197812+00:00</t>
+          <t>2026-08-11T03:54:12.123535+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-11T03:54:12.123535+00:00</t>
+          <t>2026-08-11T04:03:38.358208+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-11T04:03:38.358208+00:00</t>
+          <t>2026-08-11T06:00:16.152090+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-11T06:00:16.152090+00:00</t>
+          <t>2026-08-11T08:43:47.258883+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-11T08:43:47.258883+00:00</t>
+          <t>2026-08-11T10:09:06.949253+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Waves 29-30 · Emergent LLM Key</t>
+          <t>Waves 29-30 · LLM Key</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Wave 35 · `emergentintegrations`</t>
+          <t>Wave 35 · `pmc_lib`</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Currently console-logged; needs Emergent-managed Resend key</t>
+          <t>Currently console-logged; needs PMC-managed Resend key</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>MongoDB + FastAPI on Emergent for MVP; portability was a design constraint</t>
+          <t>MongoDB + FastAPI on Managed for MVP; portability was a design constraint</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-11T10:09:06.949253+00:00</t>
+          <t>2026-08-11T10:55:19.049176+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-11T10:55:19.049176+00:00</t>
+          <t>2026-08-11T13:00:22.219441+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-11T13:00:22.219441+00:00</t>
+          <t>2026-08-11T15:00:44.087302+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-11T15:00:44.087302+00:00</t>
+          <t>2026-08-11T15:29:48.253960+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-11T15:29:48.253960+00:00</t>
+          <t>2026-08-12T02:18:39.996436+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-12T02:18:39.996436+00:00</t>
+          <t>2026-08-12T05:29:34.468159+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-12T05:29:34.468159+00:00</t>
+          <t>2026-08-12T07:01:14.791801+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-12T07:01:14.791801+00:00</t>
+          <t>2026-08-12T10:59:55.285965+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-12T10:59:55.285965+00:00</t>
+          <t>2026-08-12T14:29:39.826341+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-12T14:29:39.826341+00:00</t>
+          <t>2026-08-14T09:58:17.930301+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-14T09:58:17.930301+00:00</t>
+          <t>2026-08-17T13:08:36.818507+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-17T13:08:36.818507+00:00</t>
+          <t>2026-08-17T14:12:39.082912+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-17T14:12:39.082912+00:00</t>
+          <t>2026-08-17T14:37:19.923701+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-17T14:37:19.923701+00:00</t>
+          <t>2026-08-17T15:42:13.665912+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-17T15:42:13.665912+00:00</t>
+          <t>2026-08-17T15:57:42.666334+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-17T15:57:42.666334+00:00</t>
+          <t>2026-08-17T16:14:30.610256+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-17T16:14:30.610256+00:00</t>
+          <t>2026-08-26T01:27:59.268328+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26T01:27:59.268328+00:00</t>
+          <t>2026-08-26T05:24:48.615146+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26T05:24:48.615146+00:00</t>
+          <t>2026-08-26T06:07:23.536478+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26T06:07:23.536478+00:00</t>
+          <t>2026-08-26T07:43:01.008725+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26T07:43:01.008725+00:00</t>
+          <t>2026-08-26T08:16:14.311664+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26T08:16:14.311664+00:00</t>
+          <t>2026-09-03T10:59:43.880281+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03T10:59:43.880281+00:00</t>
+          <t>2026-09-03T11:15:22.986203+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03T11:15:22.986203+00:00</t>
+          <t>2026-09-03T11:32:16.415336+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03T11:32:16.415336+00:00</t>
+          <t>2026-09-03T11:39:24.608550+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
+++ b/docs/reports/PMC-v2-Asked-vs-Delivered.xlsx
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03T11:39:24.608550+00:00</t>
+          <t>2026-09-03T11:59:57.838512+00:00</t>
         </is>
       </c>
     </row>
